--- a/data/ams_weekly_data/Nexlev/business_report_week27.xlsx
+++ b/data/ams_weekly_data/Nexlev/business_report_week27.xlsx
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>7077.969999999999</v>
+        <v>6180.51</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
